--- a/ET/Unity/Assets/Config/Excel/AIConfig.xlsx
+++ b/ET/Unity/Assets/Config/Excel/AIConfig.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>配置ID</t>
   </si>
@@ -82,9 +82,6 @@
     <t>最大追击距离/100</t>
   </si>
   <si>
-    <t>攻击距离/100</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
   </si>
   <si>
     <t>ChaseMaxDistance</t>
-  </si>
-  <si>
-    <t>AttackRange</t>
   </si>
   <si>
     <t>int</t>
@@ -144,13 +138,13 @@
     </r>
   </si>
   <si>
-    <t>1,4,5</t>
+    <t>1,3,4,5</t>
   </si>
   <si>
     <t>巡逻精英</t>
   </si>
   <si>
-    <t>1,2,3,4</t>
+    <t>1,2,4,5</t>
   </si>
   <si>
     <t>测试木桩</t>
@@ -1221,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M14"/>
+  <dimension ref="C1:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="8" customWidth="1"/>
@@ -1232,11 +1226,10 @@
     <col min="8" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
+    <col min="12" max="12" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13">
+    <row r="1" spans="3:12">
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1247,9 +1240,8 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="3:13">
+    <row r="2" spans="3:12">
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -1260,9 +1252,8 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1" spans="3:13">
+    <row r="3" ht="14.25" customHeight="1" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1290,86 +1281,77 @@
       <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" ht="14.25" customHeight="1" spans="3:12">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="2"/>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="3"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1" spans="3:13">
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="3" t="s">
+    <row r="5" ht="14.25" customHeight="1" spans="3:12">
+      <c r="C5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="3"/>
+      <c r="E5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="4"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1" spans="3:13">
-      <c r="C5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="3:13">
+    <row r="6" spans="3:12">
       <c r="C6" s="5">
         <v>1001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F6" s="5">
         <v>500</v>
@@ -1389,20 +1371,17 @@
       <c r="K6" s="5">
         <v>1200</v>
       </c>
-      <c r="L6" s="5">
-        <v>150</v>
-      </c>
-      <c r="M6" s="5"/>
+      <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="3:13">
+    <row r="7" spans="3:12">
       <c r="C7" s="7">
         <v>2001</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F7" s="7">
         <v>300</v>
@@ -1422,16 +1401,13 @@
       <c r="K7" s="7">
         <v>2000</v>
       </c>
-      <c r="L7" s="7">
-        <v>200</v>
-      </c>
     </row>
-    <row r="14" spans="3:13">
+    <row r="14" spans="3:12">
       <c r="C14">
         <v>99001</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E14" s="7">
         <v>1</v>
@@ -1453,9 +1429,6 @@
       </c>
       <c r="K14" s="7">
         <v>2000</v>
-      </c>
-      <c r="L14" s="7">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
